--- a/esthetician_forms/004_sugaring_intake_form--esthetician_forms.xlsx
+++ b/esthetician_forms/004_sugaring_intake_form--esthetician_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'options':_4,_'value':_'almost_every_day'}</t>
+          <t>almost_every_day</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'options': 4, 'value': 'Almost Every Day'}</t>
+          <t>Almost Every Day</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_'full_body'}</t>
+          <t>full_body</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 'Full Body'}</t>
+          <t>Full Body</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_'face'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 'Face'}</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_'back/neckline'}</t>
+          <t>back/neckline</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 'Back/Neckline'}</t>
+          <t>Back/Neckline</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'options':_4,_'value':_'eyebrow'}</t>
+          <t>eyebrow</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'options': 4, 'value': 'Eyebrow'}</t>
+          <t>Eyebrow</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'options':_5,_'value':_'bikini_line'}</t>
+          <t>bikini_line</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'options': 5, 'value': 'Bikini Line'}</t>
+          <t>Bikini Line</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'options':_6,_'value':_'lip/chin'}</t>
+          <t>lip/chin</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'options': 6, 'value': 'Lip/Chin'}</t>
+          <t>Lip/Chin</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'options':_7,_'value':_'eyelashes'}</t>
+          <t>eyelashes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'options': 7, 'value': 'Eyelashes'}</t>
+          <t>Eyelashes</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'options':_8,_'value':_'eyebrow_bumps'}</t>
+          <t>eyebrow_bumps</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'options': 8, 'value': 'Eyebrow Bumps'}</t>
+          <t>Eyebrow Bumps</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'options':_9,_'value':_'full_body/upper_lip'}</t>
+          <t>full_body/upper_lip</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'options': 9, 'value': 'Full Body/Upper Lip'}</t>
+          <t>Full Body/Upper Lip</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_'full_body'}</t>
+          <t>full_body</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 'Full Body'}</t>
+          <t>Full Body</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_'face'}</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 'Face'}</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_'back/neckline'}</t>
+          <t>back/neckline</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 'Back/Neckline'}</t>
+          <t>Back/Neckline</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'options':_4,_'value':_'eyebrow'}</t>
+          <t>eyebrow</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'options': 4, 'value': 'Eyebrow'}</t>
+          <t>Eyebrow</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'options':_5,_'value':_'eyelashes'}</t>
+          <t>eyelashes</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'options': 5, 'value': 'Eyelashes'}</t>
+          <t>Eyelashes</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'options':_6,_'value':_'eyebrow_bumps'}</t>
+          <t>eyebrow_bumps</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'options': 6, 'value': 'Eyebrow Bumps'}</t>
+          <t>Eyebrow Bumps</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_'none'}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 'None'}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_'skin_conditions'}</t>
+          <t>skin_conditions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 'Skin Conditions'}</t>
+          <t>Skin Conditions</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_'ingrown_hairs'}</t>
+          <t>ingrown_hairs</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 'Ingrown Hairs'}</t>
+          <t>Ingrown Hairs</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'options':_4,_'value':_'infection'}</t>
+          <t>infection</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'options': 4, 'value': 'Infection'}</t>
+          <t>Infection</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'options':_5,_'value':_'allergies'}</t>
+          <t>allergies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'options': 5, 'value': 'Allergies'}</t>
+          <t>Allergies</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_'no_pain'}</t>
+          <t>no_pain</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 'No Pain'}</t>
+          <t>No Pain</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_'little_pain'}</t>
+          <t>little_pain</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 'Little Pain'}</t>
+          <t>Little Pain</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_'some_pain'}</t>
+          <t>some_pain</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 'Some Pain'}</t>
+          <t>Some Pain</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'options':_4,_'value':_'a_lot_of_pain'}</t>
+          <t>a_lot_of_pain</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'options': 4, 'value': 'A Lot of Pain'}</t>
+          <t>A Lot of Pain</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_'smooth_and_silky_skin'}</t>
+          <t>smooth_and_silky_skin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': 'Smooth and Silky Skin'}</t>
+          <t>Smooth and Silky Skin</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_'reduced_hair_growth'}</t>
+          <t>reduced_hair_growth</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': 'Reduced Hair Growth'}</t>
+          <t>Reduced Hair Growth</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'options':_3,_'value':_'reduced_ingrown_hairs'}</t>
+          <t>reduced_ingrown_hairs</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'options': 3, 'value': 'Reduced Ingrown Hairs'}</t>
+          <t>Reduced Ingrown Hairs</t>
         </is>
       </c>
     </row>
@@ -1811,12 +1811,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'options':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'options': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1828,12 +1828,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'options':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'options': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
